--- a/Utilities/TestData/Contact.xlsx
+++ b/Utilities/TestData/Contact.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30318"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7A00DB2-562F-4EFB-B31B-DA51FE9CCABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F543FB1E-3518-4B6D-A633-604C49F1800E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
     <t>jiva</t>
   </si>
   <si>
-    <t xml:space="preserve">Title </t>
+    <t>Title</t>
   </si>
   <si>
     <t xml:space="preserve">test </t>
@@ -84,10 +84,10 @@
     <t>jenny</t>
   </si>
   <si>
-    <t xml:space="preserve">Date of Birth </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building Name </t>
+    <t>Date of Birth</t>
+  </si>
+  <si>
+    <t>Building Name</t>
   </si>
   <si>
     <t>Birmingham</t>
@@ -132,7 +132,7 @@
     <t>Extension</t>
   </si>
   <si>
-    <t xml:space="preserve">Mobile </t>
+    <t>Mobile</t>
   </si>
   <si>
     <t>Campaigns</t>
@@ -159,10 +159,10 @@
     <t>Business Units</t>
   </si>
   <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pager </t>
+    <t>CaterXpert</t>
+  </si>
+  <si>
+    <t>Pager</t>
   </si>
   <si>
     <t>Email</t>
@@ -245,14 +245,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -643,7 +642,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="4">
-        <v>36387</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -815,7 +814,7 @@
       <c r="A31" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="4">
         <v>46234</v>
       </c>
     </row>
